--- a/data/source/Political_Science_Journal_Word_Limits.xlsx
+++ b/data/source/Political_Science_Journal_Word_Limits.xlsx
@@ -2498,12 +2498,12 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>No detailed included/excluded component definition found.</t>
+          <t>The guidelines ask for the manuscript's word count, not exceeding 10,000 words, but do not say which parts count.</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Research articles.</t>
+          <t>Research articles; rechecked 16 October 2026. Review is double-anonymized, so the title page, which carries the word count and an author biography of up to 100 words, is a separate file. Abstract suggested at 150 words or fewer.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">

--- a/data/source/Political_Science_Journal_Word_Limits.xlsx
+++ b/data/source/Political_Science_Journal_Word_Limits.xlsx
@@ -1160,24 +1160,22 @@
           <t>Comparative politics</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C24" s="13" t="n">
+        <v>11000</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, references, figure captions, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Abstract of 200 words.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -1234,24 +1232,22 @@
           <t>Comparative politics</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C26" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, references, figure captions and endnotes.</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Research notes up to 4,000 words; abstract up to 150 words.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -1345,24 +1341,22 @@
 Political behavior, public opinion, and political psychology</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C29" s="13" t="n">
+        <v>8000</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, figure and table captions, footnotes and appendices; references are not mentioned. Figures count as 200 words per half-page figure and 400 for a large one.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Figures add 200 or 400 words each, which a word count cannot see. An online appendix has no limit.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -1981,24 +1975,22 @@
           <t>Security, conflict, and peace</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C47" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 7,000 and 10,000 words, including tables, references, figure and table captions, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Abstract of 100 words.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -2018,29 +2010,27 @@
           <t>Security, conflict, and peace</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C48" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes references, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026. A typical paper should be no more than 10,000 words, but manuscripts of up to 12,000 are accepted, for example with multiple case studies or mixed methods. Abstract of 150 words.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>https://contemporarysecuritypolicy.org/for-authors/</t>
+          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=fcsp20</t>
         </is>
       </c>
     </row>
@@ -2055,29 +2045,27 @@
           <t>Security, conflict, and peace</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C49" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 9,000 and 10,000 words, including references and footnotes.</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Abstract of 200 words.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=fint20</t>
+          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=finp20</t>
         </is>
       </c>
     </row>
@@ -2127,29 +2115,27 @@
           <t>Security, conflict, and peace</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C51" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 8,000 and 10,000 words, not including reference citations and notes.</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Original articles; Rechecked 16 October 2026. Review articles up to 12,000 words. Abstract of 200 words.</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=utpv20</t>
+          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=ftpv20</t>
         </is>
       </c>
     </row>
@@ -2164,24 +2150,22 @@
           <t>Security, conflict, and peace</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C52" s="13" t="n">
+        <v>12000</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 8,000 and 12,000 words, including the abstract, references, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026. Abstract of 100 words.</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -2201,24 +2185,22 @@
           <t>International and comparative political economy</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C53" s="13" t="n">
+        <v>12000</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, references, figure captions, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026. Pedagogical interventions run 6,000-8,000 words.</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -2238,24 +2220,22 @@
           <t>International and comparative political economy</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C54" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, references, figure and table captions, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Original articles; Rechecked 16 October 2026. Longer only in exceptional circumstances, and very rarely over 11,000 words.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -2816,24 +2796,22 @@
           <t>Political behavior, public opinion, and political psychology</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C70" s="13" t="n">
+        <v>8000</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes the abstract, tables, references, and figure and table captions; notes are not mentioned.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Original and replication articles; Rechecked 16 October 2026. Forum articles up to 3,000 words.</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -2853,29 +2831,27 @@
           <t>Political behavior, public opinion, and political psychology</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C71" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes tables, figure captions and endnotes; excludes references.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Research notes and data notes up to 5,000 words.</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://ecpr.eu/content-page/559</t>
+          <t>https://www.tandfonline.com/action/authorSubmission?show=instructions&amp;journalCode=prxx20</t>
         </is>
       </c>
     </row>
@@ -2960,24 +2936,22 @@
           <t>Political theory and political philosophy</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C74" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes figure and table captions and endnotes.</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Data notes up to 3,000 words.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -3106,22 +3080,22 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>No longer than 12,000 (preferred)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Not stated.</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026. The editors generally prefer submissions of no more than 12,000 words and may return longer papers unreviewed; 7,000-9,000 words is a good target. Letters up to 4,000 words.</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Criteria incomplete</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -3213,24 +3187,22 @@
           <t>Political theory and political philosophy</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C81" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes all text, notes and references.</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Articles and survey articles; Rechecked 16 October 2026. Ordinarily less than 10,000 words; debate pieces under 5,000. Abstract under 150 words.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -3793,7 +3765,7 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>This does not establish that the journal has no limit.</t>
+          <t>Rechecked 16 October 2026: no limit is given for research articles; Policy Insights pieces run to 3,000 words. This does not establish that the journal has no limit.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -3855,22 +3827,22 @@
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>No article-length counting definition found in the accessible instructions.</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026: the instructions point to a maximum on the journal's About page, which gives none. Abstract of 150 words. This does not establish that the journal has no limit.</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -4007,7 +3979,7 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>This does not establish that the journal has no limit.</t>
+          <t>Rechecked 16 October 2026. This does not establish that the journal has no limit.</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -4039,12 +4011,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>No article-length counting definition found in the accessible instructions.</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026: the publisher's instructions page for this journal is empty.</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -4139,24 +4111,22 @@
           <t>Gender, race, ethnicity, and identity</t>
         </is>
       </c>
-      <c r="C107" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C107" s="13" t="n">
+        <v>8750</v>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes the abstract, tables, references, figure and table captions, and endnotes.</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026.</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -4281,24 +4251,22 @@
           <t>Gender, race, ethnicity, and identity</t>
         </is>
       </c>
-      <c r="C111" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C111" s="13" t="n">
+        <v>9000</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes printed appendices and references; excludes tables, figures and online appendices.</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Standard articles; Rechecked 16 October 2026. Manuscripts over the limit are returned for adjustment. Abstract up to 200 words.</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -4462,24 +4430,22 @@
           <t>Political sociology, movements, and participation</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C116" s="13" t="n">
+        <v>8000</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Counts every word of the main document, including the title, abstract, references, tables, figures, footnotes, endnotes, appendices and captions; online-only appendices are excluded.</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Articles; Rechecked 16 October 2026. Profiles up to 3,000 words.</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -4569,24 +4535,22 @@
           <t>Environmental politics</t>
         </is>
       </c>
-      <c r="C119" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C119" s="13" t="n">
+        <v>8000</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Excludes references.</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Normally no more than 8,000 words; first submissions over 9,000 are returned. Brief reports up to 3,000 words including references.</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -4676,24 +4640,22 @@
           <t>Environmental politics</t>
         </is>
       </c>
-      <c r="C122" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C122" s="13" t="n">
+        <v>7000</v>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Not stated.</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Synthesis articles 8,000 words; policy analyses 5,000.</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Criteria incomplete</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -4855,24 +4817,22 @@
           <t>Political geography, urban, and territorial politics</t>
         </is>
       </c>
-      <c r="C127" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C127" s="13" t="n">
+        <v>9000</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Includes the abstract, tables, and figure and table captions; excludes the reference list.</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026.</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -4892,24 +4852,22 @@
           <t>Political geography, urban, and territorial politics</t>
         </is>
       </c>
-      <c r="C128" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C128" s="13" t="n">
+        <v>10000</v>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 8,000 and 10,000 words, including the abstract, references, figure and table captions, and endnotes.</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026.</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -4929,24 +4887,22 @@
           <t>Political geography, urban, and territorial politics</t>
         </is>
       </c>
-      <c r="C129" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C129" s="13" t="n">
+        <v>8000</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 6,000 and 8,000 words, including tables, references, figure and table captions, footnotes and endnotes.</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Rechecked 16 October 2026.</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -5001,24 +4957,22 @@
           <t>Religion and politics</t>
         </is>
       </c>
-      <c r="C131" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C131" s="13" t="n">
+        <v>12000</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 8,000 and 12,000 words; what counts is not stated.</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026. Data notes up to 3,000 words.</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Criteria incomplete</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -5180,24 +5134,22 @@
           <t>Human rights and global governance</t>
         </is>
       </c>
-      <c r="C136" s="13" t="inlineStr">
-        <is>
-          <t>Not verified</t>
-        </is>
+      <c r="C136" s="13" t="n">
+        <v>12000</v>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Not verified.</t>
+          <t>Between 6,000 and 12,000 words, including the abstract, tables, references, figure and table captions, and endnotes.</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Current official length and counting rules could not be verified.</t>
+          <t>Research articles; Rechecked 16 October 2026.</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Not verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
